--- a/data/2nd Round/Results Table/Mo_200Sb_25Se_Results Table.xlsx
+++ b/data/2nd Round/Results Table/Mo_200Sb_25Se_Results Table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fbdd27f2520478cf/Ambiente de Trabalho/TESE/Data_Analysis/data/2nd Round/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fbdd27f2520478cf/Ambiente de Trabalho/TESE/Data_Analysis/data/2nd Round/Results Table/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{52A1C346-B0C8-4496-BD4E-5439540D5A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{375B1E3D-952E-4B9A-BA40-B3049BCC4663}"/>
+    <workbookView xWindow="5124" yWindow="3252" windowWidth="17280" windowHeight="8880" xr2:uid="{375B1E3D-952E-4B9A-BA40-B3049BCC4663}"/>
   </bookViews>
   <sheets>
     <sheet name="Mo_200Sb_25Se_Results Table" sheetId="1" r:id="rId1"/>

--- a/data/2nd Round/Results Table/Mo_200Sb_25Se_Results Table.xlsx
+++ b/data/2nd Round/Results Table/Mo_200Sb_25Se_Results Table.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{52A1C346-B0C8-4496-BD4E-5439540D5A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5124" yWindow="3252" windowWidth="17280" windowHeight="8880" xr2:uid="{375B1E3D-952E-4B9A-BA40-B3049BCC4663}"/>
+    <workbookView xWindow="4200" yWindow="2736" windowWidth="17280" windowHeight="8880" xr2:uid="{375B1E3D-952E-4B9A-BA40-B3049BCC4663}"/>
   </bookViews>
   <sheets>
     <sheet name="Mo_200Sb_25Se_Results Table" sheetId="1" r:id="rId1"/>
